--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1011,7 +1011,7 @@
     <t>医薬品</t>
   </si>
   <si>
-    <t>投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3616" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -524,6 +524,19 @@
   <si>
     <t>依頼医を格納するための拡張。  
 依頼医を記述した Practitioner  リソースへの参照。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:uncategorizedComment</t>
@@ -595,22 +608,22 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:rpNumber.id</t>
+    <t>MedicationAdministration.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.id</t>
@@ -632,7 +645,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.extension</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.extension</t>
@@ -653,7 +666,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.use</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.use</t>
@@ -690,7 +703,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.type</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.type</t>
@@ -727,16 +740,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.system</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -745,7 +758,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -757,19 +770,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.value</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -781,7 +794,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.period</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.period</t>
@@ -806,7 +819,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.assigner</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.assigner</t>
@@ -832,63 +845,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.instantiates</t>
@@ -2299,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO105"/>
+  <dimension ref="A1:AO97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
@@ -3883,7 +3839,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3901,7 +3857,7 @@
         <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3961,10 +3917,10 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
@@ -3984,14 +3940,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4004,13 +3962,13 @@
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>170</v>
@@ -4018,12 +3976,8 @@
       <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -4071,7 +4025,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4089,7 +4043,7 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -4103,18 +4057,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>81</v>
@@ -4123,24 +4077,26 @@
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -4176,17 +4132,19 @@
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4198,16 +4156,16 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -4218,23 +4176,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -4246,16 +4202,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4293,19 +4249,17 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4320,13 +4274,13 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>79</v>
@@ -4337,12 +4291,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>79</v>
       </c>
@@ -4351,7 +4307,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -4363,15 +4319,17 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4420,28 +4378,28 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4452,21 +4410,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4478,17 +4436,15 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4525,37 +4481,37 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4569,46 +4525,44 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4632,55 +4586,55 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4688,10 +4642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4708,25 +4662,25 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4751,13 +4705,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4775,7 +4729,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4787,19 +4741,19 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4807,10 +4761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4818,7 +4772,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4833,26 +4787,26 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>79</v>
@@ -4870,13 +4824,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4894,7 +4848,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4906,19 +4860,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4926,10 +4880,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4952,24 +4906,26 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -5011,7 +4967,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5023,19 +4979,19 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -5043,10 +4999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5054,7 +5010,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -5069,15 +5025,17 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5126,7 +5084,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5138,19 +5096,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5158,10 +5116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5184,17 +5142,15 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5243,7 +5199,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5255,19 +5211,19 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5275,14 +5231,12 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>79</v>
       </c>
@@ -5291,7 +5245,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -5300,19 +5254,19 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5362,31 +5316,31 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5394,10 +5348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5408,7 +5362,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5417,16 +5371,16 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>192</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5477,25 +5431,25 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5509,14 +5463,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5532,20 +5486,18 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5582,19 +5534,19 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5606,13 +5558,13 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>195</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5626,10 +5578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5637,7 +5589,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5655,17 +5607,15 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>206</v>
+        <v>279</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5689,13 +5639,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5713,10 +5663,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5725,19 +5675,19 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5745,10 +5695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>216</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5759,7 +5709,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5768,23 +5718,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5808,13 +5754,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5832,31 +5778,31 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>214</v>
+        <v>294</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5864,10 +5810,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5875,7 +5821,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
@@ -5887,29 +5833,25 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>79</v>
@@ -5927,13 +5869,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5951,7 +5893,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5963,19 +5905,19 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5983,10 +5925,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6009,16 +5951,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6068,10 +6010,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -6080,19 +6022,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>243</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6100,10 +6042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6111,7 +6053,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -6126,13 +6068,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6183,10 +6125,10 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -6195,19 +6137,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6215,10 +6157,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6238,20 +6180,18 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6300,7 +6240,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6312,19 +6252,19 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>261</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6332,10 +6272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6355,16 +6295,16 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6415,7 +6355,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6430,13 +6370,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -6447,10 +6387,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6458,10 +6398,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6473,13 +6413,13 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6530,13 +6470,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -6545,16 +6485,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6562,10 +6502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6573,32 +6513,30 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6623,13 +6561,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6647,13 +6585,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6662,16 +6600,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6679,10 +6617,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6693,7 +6631,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6705,13 +6643,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6738,13 +6676,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6762,31 +6700,31 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>309</v>
+        <v>199</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6794,21 +6732,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6820,15 +6758,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6853,13 +6793,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6877,25 +6817,25 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6909,44 +6849,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6994,31 +6936,31 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>132</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -7026,10 +6968,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7037,7 +6979,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -7049,16 +6991,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>327</v>
+        <v>221</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7085,13 +7027,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -7109,10 +7051,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -7124,16 +7066,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -7141,10 +7083,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7152,7 +7094,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -7164,16 +7106,16 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7224,10 +7166,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7239,16 +7181,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7256,10 +7198,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7282,13 +7224,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>343</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7315,13 +7257,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7339,7 +7281,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7354,16 +7296,16 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7371,10 +7313,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7382,10 +7324,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7394,18 +7336,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7454,13 +7398,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -7469,27 +7413,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7500,7 +7444,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7509,18 +7453,20 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7569,13 +7515,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7584,16 +7530,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7601,10 +7547,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7615,7 +7561,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7627,13 +7573,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>191</v>
+        <v>398</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7684,31 +7630,31 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>195</v>
+        <v>401</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7716,14 +7662,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7742,17 +7688,15 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7801,7 +7745,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>202</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7813,13 +7757,13 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>195</v>
+        <v>408</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7833,46 +7777,42 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7920,25 +7860,25 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>412</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>132</v>
+        <v>413</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7952,10 +7892,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7978,13 +7918,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8011,13 +7951,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -8035,7 +7975,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>198</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8047,13 +7987,13 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>380</v>
+        <v>199</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -8067,10 +8007,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8078,10 +8018,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -8090,16 +8030,16 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>136</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8138,37 +8078,35 @@
         <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>381</v>
+        <v>206</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -8182,12 +8120,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8208,13 +8148,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>418</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8241,13 +8181,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8265,7 +8205,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>387</v>
+        <v>206</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8274,22 +8214,22 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8297,12 +8237,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8323,17 +8265,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8382,7 +8322,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>206</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8391,35 +8331,37 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8428,7 +8370,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8440,17 +8382,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8499,31 +8439,31 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>206</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8531,12 +8471,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8557,13 +8499,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8614,7 +8556,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>206</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8623,22 +8565,22 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8646,12 +8588,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8672,13 +8616,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8729,7 +8673,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>206</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8738,16 +8682,16 @@
         <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8761,42 +8705,46 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="M56" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8844,25 +8792,25 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>424</v>
+        <v>358</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>427</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>132</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8876,10 +8824,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8902,13 +8850,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>444</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8959,7 +8907,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>194</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8971,13 +8919,13 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>195</v>
+        <v>445</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8991,10 +8939,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9005,7 +8953,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -9017,15 +8965,17 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>135</v>
+        <v>447</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9050,53 +9000,53 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>79</v>
+        <v>450</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>202</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>79</v>
+        <v>452</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9104,14 +9054,12 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9120,7 +9068,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9132,13 +9080,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>433</v>
+        <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>196</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
+        <v>197</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9189,25 +9137,25 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9221,16 +9169,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9249,15 +9195,17 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>202</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9294,19 +9242,19 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9315,7 +9263,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>147</v>
@@ -9324,7 +9272,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9338,13 +9286,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9366,13 +9314,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9423,7 +9371,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9432,7 +9380,7 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>147</v>
@@ -9455,13 +9403,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>79</v>
@@ -9483,13 +9431,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9540,7 +9488,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9549,7 +9497,7 @@
         <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>147</v>
@@ -9572,14 +9520,12 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9597,19 +9543,23 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9657,7 +9607,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9666,22 +9616,22 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9689,45 +9639,45 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>371</v>
+        <v>475</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>372</v>
+        <v>476</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>172</v>
+        <v>477</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>173</v>
+        <v>478</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9776,31 +9726,31 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>373</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>132</v>
+        <v>480</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9808,10 +9758,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9834,13 +9784,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9867,13 +9817,11 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9891,7 +9839,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9909,13 +9857,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9923,10 +9871,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9949,17 +9897,15 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>462</v>
+        <v>196</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9984,11 +9930,13 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -10006,7 +9954,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>461</v>
+        <v>198</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10018,19 +9966,19 @@
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>466</v>
+        <v>199</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>467</v>
+        <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10038,21 +9986,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -10064,15 +10012,17 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10109,37 +10059,37 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -10153,14 +10103,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="D68" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10179,17 +10131,15 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>492</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>198</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10226,19 +10176,19 @@
         <v>79</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10256,7 +10206,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10270,14 +10220,12 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10295,19 +10243,23 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10355,7 +10307,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10367,19 +10319,19 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10387,14 +10339,12 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10403,7 +10353,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10412,19 +10362,23 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10472,31 +10426,31 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>202</v>
+        <v>479</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>79</v>
+        <v>480</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10504,10 +10458,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10518,7 +10472,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -10527,22 +10481,22 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>481</v>
+        <v>221</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10567,13 +10521,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10591,31 +10545,31 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10623,10 +10577,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10646,23 +10600,19 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>490</v>
+        <v>196</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10710,7 +10660,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>494</v>
+        <v>198</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10722,19 +10672,19 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>495</v>
+        <v>199</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>496</v>
+        <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10742,21 +10692,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10768,15 +10718,17 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>498</v>
+        <v>202</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10801,53 +10753,55 @@
         <v>79</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>497</v>
+        <v>206</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>501</v>
+        <v>199</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>502</v>
+        <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10855,12 +10809,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>79</v>
       </c>
@@ -10869,7 +10825,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10881,13 +10837,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>191</v>
+        <v>509</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>192</v>
+        <v>510</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>193</v>
+        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10938,25 +10894,25 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -10970,14 +10926,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10993,21 +10949,23 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>134</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>198</v>
+        <v>467</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>199</v>
+        <v>468</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11043,11 +11001,9 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11055,7 +11011,7 @@
         <v>138</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11067,19 +11023,19 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>195</v>
+        <v>472</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11087,13 +11043,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11103,7 +11059,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -11112,19 +11068,23 @@
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
       </c>
@@ -11148,13 +11108,11 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>79</v>
+        <v>519</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -11172,7 +11130,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11184,19 +11142,19 @@
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11204,10 +11162,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11218,7 +11176,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -11227,23 +11185,19 @@
         <v>79</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>481</v>
+        <v>195</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11291,31 +11245,31 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>486</v>
+        <v>198</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>487</v>
+        <v>199</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>488</v>
+        <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11323,21 +11277,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11346,23 +11300,21 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>490</v>
+        <v>202</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>491</v>
+        <v>203</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
@@ -11398,43 +11350,43 @@
         <v>79</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>206</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>495</v>
+        <v>199</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>496</v>
+        <v>79</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11442,10 +11394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11453,7 +11405,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -11465,29 +11417,29 @@
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>79</v>
+        <v>530</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>79</v>
@@ -11505,13 +11457,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>516</v>
+        <v>79</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>517</v>
+        <v>79</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11529,7 +11481,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11541,19 +11493,19 @@
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -11561,10 +11513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11584,18 +11536,20 @@
         <v>79</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11644,7 +11598,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>194</v>
+        <v>539</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11656,19 +11610,19 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>195</v>
+        <v>540</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>79</v>
+        <v>541</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11676,21 +11630,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11699,21 +11653,21 @@
         <v>79</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>198</v>
+        <v>544</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
       </c>
@@ -11749,43 +11703,43 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>202</v>
+        <v>547</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>195</v>
+        <v>548</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>79</v>
+        <v>549</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11793,14 +11747,12 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11809,7 +11761,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11818,19 +11770,21 @@
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>524</v>
+        <v>195</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>525</v>
+        <v>552</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11878,31 +11832,31 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>202</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>79</v>
+        <v>556</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>79</v>
+        <v>557</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -11910,10 +11864,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11924,7 +11878,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>79</v>
@@ -11936,19 +11890,19 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>481</v>
+        <v>560</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>561</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
+        <v>562</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>484</v>
+        <v>563</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>485</v>
+        <v>564</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -11985,41 +11939,43 @@
         <v>79</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AC83" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>486</v>
+        <v>565</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>487</v>
+        <v>566</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>488</v>
+        <v>567</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12027,13 +11983,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>528</v>
+        <v>568</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>529</v>
+        <v>569</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -12055,19 +12011,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>530</v>
+        <v>570</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>531</v>
+        <v>571</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12096,7 +12052,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12114,7 +12070,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12126,19 +12082,19 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12146,10 +12102,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12172,13 +12128,13 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12229,7 +12185,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12247,7 +12203,7 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>
@@ -12261,14 +12217,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12290,13 +12246,13 @@
         <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12337,7 +12293,7 @@
         <v>137</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
@@ -12346,7 +12302,7 @@
         <v>138</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12364,7 +12320,7 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>79</v>
@@ -12378,10 +12334,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>539</v>
+        <v>575</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12407,23 +12363,23 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>79</v>
@@ -12465,7 +12421,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12477,19 +12433,19 @@
         <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12497,10 +12453,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12523,16 +12479,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12582,7 +12538,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12594,19 +12550,19 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12614,10 +12570,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12643,14 +12599,14 @@
         <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12699,7 +12655,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12711,19 +12667,19 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -12731,10 +12687,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12757,17 +12713,17 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12816,7 +12772,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12828,19 +12784,19 @@
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -12848,10 +12804,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12874,19 +12830,19 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -12935,7 +12891,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12947,19 +12903,19 @@
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -12967,14 +12923,12 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>79</v>
       </c>
@@ -12995,19 +12949,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>481</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O92" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13032,11 +12986,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>587</v>
+        <v>79</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13054,31 +13010,31 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13086,10 +13042,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>536</v>
+        <v>586</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13112,15 +13068,17 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>191</v>
+        <v>587</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>192</v>
+        <v>588</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13169,7 +13127,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>194</v>
+        <v>586</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13178,22 +13136,22 @@
         <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>79</v>
+        <v>591</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>195</v>
+        <v>592</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>79</v>
+        <v>593</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13201,21 +13159,21 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>79</v>
@@ -13227,16 +13185,16 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>134</v>
+        <v>595</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>198</v>
+        <v>596</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>199</v>
+        <v>597</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>200</v>
+        <v>598</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13274,43 +13232,41 @@
         <v>79</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>138</v>
+        <v>600</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>202</v>
+        <v>594</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>195</v>
+        <v>601</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>79</v>
+        <v>602</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13318,18 +13274,20 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>89</v>
@@ -13341,29 +13299,27 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>103</v>
+        <v>605</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>541</v>
+        <v>606</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>542</v>
+        <v>606</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>591</v>
+        <v>79</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>79</v>
@@ -13405,7 +13361,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13414,22 +13370,22 @@
         <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>213</v>
+        <v>608</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>547</v>
+        <v>609</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>548</v>
+        <v>132</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13437,12 +13393,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>79</v>
       </c>
@@ -13460,19 +13418,19 @@
         <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>191</v>
+        <v>612</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>551</v>
+        <v>613</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>552</v>
+        <v>613</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>553</v>
+        <v>614</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13522,7 +13480,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>554</v>
+        <v>594</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13531,22 +13489,22 @@
         <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>213</v>
+        <v>591</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>79</v>
@@ -13554,10 +13512,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>558</v>
+        <v>615</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13568,7 +13526,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13577,21 +13535,21 @@
         <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>109</v>
+        <v>616</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>559</v>
+        <v>617</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -13639,975 +13597,33 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>562</v>
+        <v>615</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>563</v>
+        <v>620</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>564</v>
+        <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AC102" s="2"/>
-      <c r="AD102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="D103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="D104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO105" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3616" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -524,19 +524,6 @@
   <si>
     <t>依頼医を格納するための拡張。  
 依頼医を記述した Practitioner  リソースへの参照。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:uncategorizedComment</t>
@@ -608,22 +595,22 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
+    <t>MedicationAdministration.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.id</t>
@@ -645,7 +632,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
+    <t>MedicationAdministration.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.extension</t>
@@ -666,7 +653,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
+    <t>MedicationAdministration.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.use</t>
@@ -703,7 +690,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
+    <t>MedicationAdministration.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.type</t>
@@ -740,16 +727,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
+    <t>MedicationAdministration.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -758,7 +745,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -770,19 +757,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
+    <t>MedicationAdministration.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -794,7 +781,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
+    <t>MedicationAdministration.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.period</t>
@@ -819,7 +806,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
+    <t>MedicationAdministration.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.assigner</t>
@@ -845,6 +832,63 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.instantiates</t>
@@ -2255,7 +2299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO97"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
@@ -3839,7 +3883,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3857,7 +3901,7 @@
         <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3917,10 +3961,10 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
@@ -3940,16 +3984,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C15" t="s" s="2">
         <v>168</v>
       </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3962,13 +4004,13 @@
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>170</v>
@@ -3976,8 +4018,12 @@
       <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="N15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -4025,7 +4071,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4043,7 +4089,7 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -4057,18 +4103,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>81</v>
@@ -4077,26 +4123,24 @@
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -4132,19 +4176,17 @@
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4156,16 +4198,16 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -4176,21 +4218,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="D17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -4202,16 +4246,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4249,17 +4293,19 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4274,13 +4320,13 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>79</v>
@@ -4291,14 +4337,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>79</v>
       </c>
@@ -4307,7 +4351,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -4319,17 +4363,15 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4378,28 +4420,28 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4410,21 +4452,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4436,15 +4478,17 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4481,37 +4525,37 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4525,44 +4569,46 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4586,55 +4632,55 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4642,10 +4688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4662,25 +4708,25 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4705,13 +4751,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4729,7 +4775,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4741,19 +4787,19 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4761,10 +4807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4772,7 +4818,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4787,26 +4833,26 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>79</v>
@@ -4824,13 +4870,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4848,7 +4894,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4860,19 +4906,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4880,10 +4926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4906,26 +4952,24 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4967,7 +5011,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4979,19 +5023,19 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4999,10 +5043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5010,7 +5054,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -5025,17 +5069,15 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5084,7 +5126,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5096,19 +5138,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5116,10 +5158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5142,15 +5184,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5199,7 +5243,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5211,19 +5255,19 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5231,12 +5275,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
       </c>
@@ -5245,7 +5291,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -5254,19 +5300,19 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5316,31 +5362,31 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>182</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5348,10 +5394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5362,7 +5408,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5371,16 +5417,16 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>192</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>193</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5431,25 +5477,25 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>194</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5463,14 +5509,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5486,18 +5532,20 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>198</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5534,19 +5582,19 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5558,13 +5606,13 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5578,10 +5626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5589,7 +5637,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5607,15 +5655,17 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5639,13 +5689,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>282</v>
+        <v>211</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5663,10 +5713,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5675,19 +5725,19 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5695,10 +5745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5709,7 +5759,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5718,19 +5768,23 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5754,13 +5808,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5778,31 +5832,31 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>294</v>
+        <v>214</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5810,10 +5864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5821,7 +5875,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
@@ -5833,25 +5887,29 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>79</v>
@@ -5869,13 +5927,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5893,7 +5951,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5905,19 +5963,19 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5925,10 +5983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5951,16 +6009,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6010,10 +6068,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -6022,19 +6080,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -6042,10 +6100,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6053,7 +6111,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -6068,13 +6126,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>248</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6125,10 +6183,10 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -6137,19 +6195,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>252</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6157,10 +6215,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6180,18 +6238,20 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>255</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6240,7 +6300,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6252,19 +6312,19 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>260</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6272,10 +6332,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6295,16 +6355,16 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6355,7 +6415,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6370,13 +6430,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>331</v>
+        <v>285</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -6387,10 +6447,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6398,10 +6458,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6413,13 +6473,13 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6470,13 +6530,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -6485,16 +6545,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6502,10 +6562,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6513,30 +6573,32 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6561,13 +6623,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6585,13 +6647,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6600,16 +6662,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6617,10 +6679,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6631,7 +6693,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6643,13 +6705,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6676,13 +6738,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6700,31 +6762,31 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>198</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6732,21 +6794,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6758,17 +6820,15 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6793,13 +6853,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6817,25 +6877,25 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6849,46 +6909,44 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6936,31 +6994,31 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6968,10 +7026,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6979,7 +7037,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -6991,16 +7049,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7027,13 +7085,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -7051,10 +7109,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -7066,16 +7124,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -7083,10 +7141,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7094,7 +7152,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -7106,16 +7164,16 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7166,10 +7224,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7181,16 +7239,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7198,10 +7256,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7224,13 +7282,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>343</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7257,13 +7315,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7281,7 +7339,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7296,16 +7354,16 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7313,10 +7371,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7324,10 +7382,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7336,20 +7394,18 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7398,13 +7454,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -7413,27 +7469,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7444,7 +7500,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7453,20 +7509,18 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7515,13 +7569,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7530,16 +7584,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7547,10 +7601,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7561,7 +7615,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7573,13 +7627,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>398</v>
+        <v>191</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7630,31 +7684,31 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>397</v>
+        <v>194</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>401</v>
+        <v>195</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7662,14 +7716,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7688,15 +7742,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>404</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7745,7 +7801,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>202</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7757,13 +7813,13 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>408</v>
+        <v>195</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7777,42 +7833,46 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7860,25 +7920,25 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>412</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>413</v>
+        <v>132</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7892,10 +7952,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7918,13 +7978,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7951,13 +8011,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7975,7 +8035,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7987,13 +8047,13 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>199</v>
+        <v>380</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -8007,10 +8067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8018,10 +8078,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -8030,16 +8090,16 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>382</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>135</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>136</v>
+        <v>384</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8078,35 +8138,37 @@
         <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>206</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -8120,14 +8182,12 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8148,13 +8208,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>418</v>
+        <v>217</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8181,13 +8241,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8205,7 +8265,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>206</v>
+        <v>387</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8214,22 +8274,22 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8237,14 +8297,12 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8265,15 +8323,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8322,7 +8382,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>206</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8331,37 +8391,35 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8370,7 +8428,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8382,15 +8440,17 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>405</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8439,31 +8499,31 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>206</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8471,14 +8531,12 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8499,13 +8557,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8556,7 +8614,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>206</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8565,22 +8623,22 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8588,14 +8646,12 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8616,13 +8672,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8673,7 +8729,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>206</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8682,16 +8738,16 @@
         <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>79</v>
+        <v>423</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8705,46 +8761,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>356</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>356</v>
+        <v>425</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8792,25 +8844,25 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>358</v>
+        <v>424</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>427</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>132</v>
+        <v>428</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8824,10 +8876,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8850,13 +8902,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>443</v>
+        <v>364</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>444</v>
+        <v>365</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8907,7 +8959,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>194</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8919,13 +8971,13 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>445</v>
+        <v>195</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8939,10 +8991,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8953,7 +9005,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8965,17 +9017,15 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>447</v>
+        <v>135</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9000,53 +9050,53 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>446</v>
+        <v>202</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9054,12 +9104,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9068,7 +9120,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9080,13 +9132,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>195</v>
+        <v>433</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>196</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>197</v>
+        <v>435</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9137,25 +9189,25 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9169,14 +9221,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="D60" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9195,17 +9249,15 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>202</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9242,19 +9294,19 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9263,7 +9315,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>147</v>
@@ -9272,7 +9324,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9286,13 +9338,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9314,13 +9366,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9371,7 +9423,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9380,7 +9432,7 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>147</v>
@@ -9403,13 +9455,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>79</v>
@@ -9431,13 +9483,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9488,7 +9540,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9497,7 +9549,7 @@
         <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>147</v>
@@ -9520,12 +9572,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9543,23 +9597,19 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9607,7 +9657,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9616,22 +9666,22 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9639,45 +9689,45 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>475</v>
+        <v>371</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>476</v>
+        <v>372</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>477</v>
+        <v>172</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>478</v>
+        <v>173</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9726,31 +9776,31 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>373</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>480</v>
+        <v>132</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9758,10 +9808,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9784,13 +9834,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9817,11 +9867,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9839,7 +9891,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9857,13 +9909,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9871,10 +9923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9897,15 +9949,17 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>196</v>
+        <v>462</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9930,13 +9984,11 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -9954,7 +10006,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>198</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9966,19 +10018,19 @@
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>199</v>
+        <v>466</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9986,21 +10038,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -10012,17 +10064,15 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10059,37 +10109,37 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -10103,16 +10153,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10131,15 +10179,17 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>492</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>493</v>
+        <v>198</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10176,19 +10226,19 @@
         <v>79</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10206,7 +10256,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10220,12 +10270,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10243,23 +10295,19 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10307,7 +10355,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10319,19 +10367,19 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10339,12 +10387,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10353,7 +10403,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10362,23 +10412,19 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>195</v>
+        <v>477</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10426,31 +10472,31 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>479</v>
+        <v>202</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>480</v>
+        <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10458,10 +10504,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10472,7 +10518,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -10481,22 +10527,22 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>221</v>
+        <v>481</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10521,13 +10567,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>502</v>
+        <v>79</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10545,31 +10591,31 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10577,10 +10623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10600,19 +10646,23 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>196</v>
+        <v>490</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10660,7 +10710,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>198</v>
+        <v>494</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10672,19 +10722,19 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>199</v>
+        <v>495</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10692,21 +10742,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10718,17 +10768,15 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>202</v>
+        <v>498</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10753,55 +10801,53 @@
         <v>79</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>206</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>199</v>
+        <v>501</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10809,14 +10855,12 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>79</v>
       </c>
@@ -10825,7 +10869,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10837,13 +10881,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>509</v>
+        <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>510</v>
+        <v>192</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>511</v>
+        <v>193</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10894,25 +10938,25 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -10926,14 +10970,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10949,23 +10993,21 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>466</v>
+        <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>467</v>
+        <v>198</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>468</v>
+        <v>199</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11001,9 +11043,11 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11011,7 +11055,7 @@
         <v>138</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11023,19 +11067,19 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>472</v>
+        <v>195</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11043,13 +11087,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11059,7 +11103,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -11068,23 +11112,19 @@
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
       </c>
@@ -11108,11 +11148,13 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>519</v>
+        <v>79</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -11130,7 +11172,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11142,19 +11184,19 @@
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11162,10 +11204,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11176,7 +11218,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -11185,19 +11227,23 @@
         <v>79</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>195</v>
+        <v>481</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11245,31 +11291,31 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>198</v>
+        <v>486</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>199</v>
+        <v>487</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>79</v>
+        <v>488</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11277,21 +11323,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11300,21 +11346,23 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>202</v>
+        <v>490</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>203</v>
+        <v>491</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
@@ -11350,43 +11398,43 @@
         <v>79</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>206</v>
+        <v>494</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>199</v>
+        <v>495</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11394,10 +11442,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11405,7 +11453,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -11417,29 +11465,29 @@
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>103</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>530</v>
+        <v>79</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>79</v>
@@ -11457,13 +11505,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>79</v>
+        <v>516</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>79</v>
+        <v>517</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11481,7 +11529,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11493,19 +11541,19 @@
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -11513,10 +11561,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11536,20 +11584,18 @@
         <v>79</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>536</v>
+        <v>192</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11598,7 +11644,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>539</v>
+        <v>194</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11610,19 +11656,19 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>540</v>
+        <v>195</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>541</v>
+        <v>79</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11630,21 +11676,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11653,21 +11699,21 @@
         <v>79</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>544</v>
+        <v>198</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>79</v>
       </c>
@@ -11703,43 +11749,43 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>547</v>
+        <v>202</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>548</v>
+        <v>195</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11747,12 +11793,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11761,7 +11809,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11770,21 +11818,19 @@
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>195</v>
+        <v>524</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>554</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11832,31 +11878,31 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>555</v>
+        <v>202</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>556</v>
+        <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>557</v>
+        <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -11864,10 +11910,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>558</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11878,7 +11924,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>79</v>
@@ -11890,19 +11936,19 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>560</v>
+        <v>481</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>561</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>562</v>
+        <v>483</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>563</v>
+        <v>484</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>564</v>
+        <v>485</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -11939,43 +11985,41 @@
         <v>79</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>565</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>566</v>
+        <v>487</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>567</v>
+        <v>488</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -11983,13 +12027,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>568</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>569</v>
+        <v>529</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -12011,19 +12055,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>571</v>
+        <v>531</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12052,7 +12096,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>572</v>
+        <v>534</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12070,7 +12114,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12082,19 +12126,19 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12102,10 +12146,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>573</v>
+        <v>535</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12128,13 +12172,13 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12185,7 +12229,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12203,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>
@@ -12217,14 +12261,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12246,13 +12290,13 @@
         <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12293,7 +12337,7 @@
         <v>137</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
@@ -12302,7 +12346,7 @@
         <v>138</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12320,7 +12364,7 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>79</v>
@@ -12334,10 +12378,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12363,23 +12407,23 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>576</v>
+        <v>545</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>79</v>
@@ -12421,7 +12465,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12433,19 +12477,19 @@
         <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12453,10 +12497,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12479,16 +12523,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12538,7 +12582,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12550,19 +12594,19 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12570,10 +12614,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12599,14 +12643,14 @@
         <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12655,7 +12699,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12667,19 +12711,19 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -12687,10 +12731,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12713,17 +12757,17 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12772,7 +12816,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12784,19 +12828,19 @@
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>79</v>
@@ -12804,10 +12848,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12830,19 +12874,19 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -12891,7 +12935,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12903,19 +12947,19 @@
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -12923,12 +12967,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>79</v>
       </c>
@@ -12949,19 +12995,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>195</v>
+        <v>481</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>584</v>
+        <v>532</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>585</v>
+        <v>533</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12986,13 +13032,11 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>79</v>
+        <v>587</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13010,31 +13054,31 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13042,10 +13086,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>586</v>
+        <v>536</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13068,17 +13112,15 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>587</v>
+        <v>191</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>588</v>
+        <v>192</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13127,7 +13169,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>586</v>
+        <v>194</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13136,22 +13178,22 @@
         <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>591</v>
+        <v>79</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>592</v>
+        <v>195</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>593</v>
+        <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13159,21 +13201,21 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>594</v>
+        <v>538</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>79</v>
@@ -13185,16 +13227,16 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>595</v>
+        <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>596</v>
+        <v>198</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>597</v>
+        <v>199</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>598</v>
+        <v>200</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13232,41 +13274,43 @@
         <v>79</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>600</v>
+        <v>138</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>594</v>
+        <v>202</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>601</v>
+        <v>195</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>602</v>
+        <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13274,20 +13318,18 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>89</v>
@@ -13299,27 +13341,29 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>605</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>606</v>
+        <v>541</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>606</v>
+        <v>542</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>79</v>
+        <v>591</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>79</v>
@@ -13361,7 +13405,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>594</v>
+        <v>546</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13370,22 +13414,22 @@
         <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>608</v>
+        <v>213</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>609</v>
+        <v>547</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>132</v>
+        <v>548</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13393,14 +13437,12 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>611</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>79</v>
       </c>
@@ -13418,19 +13460,19 @@
         <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>612</v>
+        <v>191</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>613</v>
+        <v>551</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>613</v>
+        <v>552</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>614</v>
+        <v>553</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13480,7 +13522,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13489,22 +13531,22 @@
         <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>591</v>
+        <v>213</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>79</v>
@@ -13512,10 +13554,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13526,7 +13568,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13535,21 +13577,21 @@
         <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>616</v>
+        <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>617</v>
+        <v>559</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -13597,33 +13639,975 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AC102" s="2"/>
+      <c r="AD102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE102" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
+      <c r="AF102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
+      <c r="H105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AK105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -736,7 +736,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -745,7 +745,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -870,7 +870,7 @@
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.value</t>
@@ -1715,7 +1715,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1839,7 +1839,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1854,7 +1854,7 @@
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -268,11 +268,11 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,13 +410,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -472,7 +472,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -552,7 +552,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -659,22 +659,22 @@
     <t>MedicationAdministration.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -683,7 +683,7 @@
     <t>Identifier.use</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -700,22 +700,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -739,10 +739,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -794,7 +794,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -819,10 +819,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -846,7 +846,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -864,7 +864,7 @@
     <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -879,10 +879,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.period</t>
@@ -1041,7 +1041,7 @@
 </t>
   </si>
   <si>
-    <t>「誰が薬を受け取りましたか？」(dare ga kusuri o uketorimashita ka?)</t>
+    <t>「誰が薬を受け取りましたか？」</t>
   </si>
   <si>
     <t>薬を受け取る人、動物、またはグループ。 (Kusuri wo uketoru hito, doubutsu, matawa guruupu.)</t>
@@ -1069,7 +1069,7 @@
     <t>「エピソード・オブ・ケア」は、「エンカウンター」として提供されます。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。」</t>
+    <t>薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1091,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>「管理をサポートするための追加情報」</t>
+    <t>管理をサポートするための追加情報</t>
   </si>
   <si>
     <t>薬の投与を補助する追加情報（例えば、患者の身長や体重）。</t>
@@ -1107,10 +1107,10 @@
 Period</t>
   </si>
   <si>
-    <t>「管理の開始時刻と終了時刻」(Kanri no kaishi jikoku to shūryō jikoku)</t>
-  </si>
-  <si>
-    <t>「与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。」</t>
+    <t>「管理の開始時刻と終了時刻」</t>
+  </si>
+  <si>
+    <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1132,10 +1132,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰で、何をしたのか？」</t>
-  </si>
-  <si>
-    <t>「薬の投与を行った人や物、および彼らがどのように関与したかを示す。」</t>
+    <t>薬剤投与を行ったのは誰で、何をしたのか？</t>
+  </si>
+  <si>
+    <t>薬の投与を行った人や物、および彼らがどのように関与したかを示す。</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1165,7 +1165,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1175,11 +1175,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1188,13 +1188,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」(Pafōmansu no shurui)</t>
+    <t>「パフォーマンスの種類」</t>
   </si>
   <si>
     <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
   </si>
   <si>
-    <t>「薬物管理を行った個人の役割を説明するコード」</t>
+    <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1213,10 +1213,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」(Yakuzaiteiyogyou o okonatta no wa dare desu ka?)</t>
-  </si>
-  <si>
-    <t>「薬剤投与を行った人物または物品を示す」</t>
+    <t>「薬剤投与を行ったのは誰ですか？」</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1234,7 +1234,7 @@
     <t>与えられた薬を説明するコード。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
+    <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1256,13 +1256,13 @@
 </t>
   </si>
   <si>
-    <t>「薬が投与された理由を支持する状態または観察」</t>
+    <t>薬が投与された理由を支持する状態または観察</t>
   </si>
   <si>
     <t>薬剤が投与された理由を支持する状態または観察。</t>
   </si>
   <si>
-    <t>「これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。」</t>
+    <t>これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1287,10 +1287,10 @@
     <t>"リクエスト管理対象として実行してください。" (Rikuesuto kanri taishou toshite jikkou shite kudasai.)</t>
   </si>
   <si>
-    <t>「管理を実行するための元の要求、指示、または権限。」</t>
-  </si>
-  <si>
-    <t>「これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。」</t>
+    <t>管理を実行するための元の要求、指示、または権限。</t>
+  </si>
+  <si>
+    <t>これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1309,7 +1309,7 @@
 </t>
   </si>
   <si>
-    <t>「投与するための装置」(touyo suru tame no souchi)</t>
+    <t>投与するための装置</t>
   </si>
   <si>
     <t>患者に薬剤を投与するのに使われる装置。例えば、特定の注入ポンプ。</t>
@@ -1328,10 +1328,10 @@
 </t>
   </si>
   <si>
-    <t>「行政に関する情報」(Gyōsei ni kansuru jōhō)</t>
-  </si>
-  <si>
-    <t>「他の属性では伝えられない薬剤投与に関する追加情報」</t>
+    <t>「行政に関する情報」</t>
+  </si>
+  <si>
+    <t>他の属性では伝えられない薬剤投与に関する追加情報</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1627,7 +1627,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
@@ -1900,7 +1900,7 @@
     <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1956,7 +1956,7 @@
     <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -2326,7 +2326,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -268,11 +268,11 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
-  </si>
-  <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -355,7 +355,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト要約</t>
-  </si>
-  <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「人間の解釈のためのリソースのテキスト要約」</t>
+  </si>
+  <si>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -413,10 +413,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -549,10 +549,10 @@
 user content</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -846,7 +846,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -1044,7 +1044,7 @@
     <t>「誰が薬を受け取りましたか？」</t>
   </si>
   <si>
-    <t>薬を受け取る人、動物、またはグループ。 (Kusuri wo uketoru hito, doubutsu, matawa guruupu.)</t>
+    <t>薬を受け取る人、動物、またはグループ。</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1069,7 +1069,7 @@
     <t>「エピソード・オブ・ケア」は、「エンカウンター」として提供されます。</t>
   </si>
   <si>
-    <t>薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。</t>
+    <t>「薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。」</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1091,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>管理をサポートするための追加情報</t>
+    <t>「管理をサポートするための追加情報」</t>
   </si>
   <si>
     <t>薬の投与を補助する追加情報（例えば、患者の身長や体重）。</t>
@@ -1110,7 +1110,7 @@
     <t>「管理の開始時刻と終了時刻」</t>
   </si>
   <si>
-    <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。</t>
+    <t>「与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。」</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1132,10 +1132,10 @@
 </t>
   </si>
   <si>
-    <t>薬剤投与を行ったのは誰で、何をしたのか？</t>
-  </si>
-  <si>
-    <t>薬の投与を行った人や物、および彼らがどのように関与したかを示す。</t>
+    <t>「薬剤投与を行ったのは誰で、何をしたのか？」</t>
+  </si>
+  <si>
+    <t>「薬の投与を行った人や物、および彼らがどのように関与したかを示す。」</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1165,7 +1165,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1175,11 +1175,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>認識されなくても無視できない拡張機能</t>
-  </si>
-  <si>
-    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
+    <t>「認識されなくても無視できない拡張機能」</t>
+  </si>
+  <si>
+    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1191,10 +1191,10 @@
     <t>「パフォーマンスの種類」</t>
   </si>
   <si>
-    <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
-  </si>
-  <si>
-    <t>薬物管理を行った個人の役割を説明するコード</t>
+    <t>演者の医薬品投与における関与タイプを区別します。</t>
+  </si>
+  <si>
+    <t>「薬物管理を行った個人の役割を説明するコード」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1216,7 +1216,7 @@
     <t>「薬剤投与を行ったのは誰ですか？」</t>
   </si>
   <si>
-    <t>薬剤投与を行った人物または物品を示す</t>
+    <t>「薬剤投与を行った人物または物品を示す」</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1228,13 +1228,13 @@
     <t>MedicationAdministration.reasonCode</t>
   </si>
   <si>
-    <t>理由に基づく行政処理 (Riyuu ni motozuku gyousei shori)</t>
+    <t xml:space="preserve">理由に基づく行政処理 </t>
   </si>
   <si>
     <t>与えられた薬を説明するコード。</t>
   </si>
   <si>
-    <t>薬剤投与が行われた理由を示すコードのセット。</t>
+    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1256,13 +1256,13 @@
 </t>
   </si>
   <si>
-    <t>薬が投与された理由を支持する状態または観察</t>
+    <t>「薬が投与された理由を支持する状態または観察」</t>
   </si>
   <si>
     <t>薬剤が投与された理由を支持する状態または観察。</t>
   </si>
   <si>
-    <t>これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。</t>
+    <t>「これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。」</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1287,10 +1287,10 @@
     <t>"リクエスト管理対象として実行してください。" (Rikuesuto kanri taishou toshite jikkou shite kudasai.)</t>
   </si>
   <si>
-    <t>管理を実行するための元の要求、指示、または権限。</t>
-  </si>
-  <si>
-    <t>これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。</t>
+    <t>「管理を実行するための元の要求、指示、または権限。」</t>
+  </si>
+  <si>
+    <t>「これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。」</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1309,7 +1309,7 @@
 </t>
   </si>
   <si>
-    <t>投与するための装置</t>
+    <t>「投与するための装置」</t>
   </si>
   <si>
     <t>患者に薬剤を投与するのに使われる装置。例えば、特定の注入ポンプ。</t>
@@ -1331,7 +1331,7 @@
     <t>「行政に関する情報」</t>
   </si>
   <si>
-    <t>他の属性では伝えられない薬剤投与に関する追加情報</t>
+    <t>「他の属性では伝えられない薬剤投与に関する追加情報」</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1627,7 +1627,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
+    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -268,11 +268,11 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
-  </si>
-  <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,13 +410,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -549,10 +549,10 @@
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -846,7 +846,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -968,7 +968,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>"医薬品投与が取り消された理由を示すコードのセット"</t>
+    <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
@@ -1041,7 +1041,7 @@
 </t>
   </si>
   <si>
-    <t>「誰が薬を受け取りましたか？」</t>
+    <t>誰が薬を受け取りましたか？</t>
   </si>
   <si>
     <t>薬を受け取る人、動物、またはグループ。</t>
@@ -1069,7 +1069,7 @@
     <t>「エピソード・オブ・ケア」は、「エンカウンター」として提供されます。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。」</t>
+    <t>薬剤投与が行われた患者と医療提供者の間での訪問、入院、またはその他の接触。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1091,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>「管理をサポートするための追加情報」</t>
+    <t>管理をサポートするための追加情報</t>
   </si>
   <si>
     <t>薬の投与を補助する追加情報（例えば、患者の身長や体重）。</t>
@@ -1107,10 +1107,10 @@
 Period</t>
   </si>
   <si>
-    <t>「管理の開始時刻と終了時刻」</t>
-  </si>
-  <si>
-    <t>「与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。」</t>
+    <t>管理の開始時刻と終了時刻</t>
+  </si>
+  <si>
+    <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1132,10 +1132,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰で、何をしたのか？」</t>
-  </si>
-  <si>
-    <t>「薬の投与を行った人や物、および彼らがどのように関与したかを示す。」</t>
+    <t>薬剤投与を行ったのは誰で、何をしたのか？</t>
+  </si>
+  <si>
+    <t>薬の投与を行った人や物、および彼らがどのように関与したかを示す。</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1165,7 +1165,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1175,11 +1175,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1188,13 +1188,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」</t>
+    <t>パフォーマンスの種類</t>
   </si>
   <si>
     <t>演者の医薬品投与における関与タイプを区別します。</t>
   </si>
   <si>
-    <t>「薬物管理を行った個人の役割を説明するコード」</t>
+    <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1213,10 +1213,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」</t>
-  </si>
-  <si>
-    <t>「薬剤投与を行った人物または物品を示す」</t>
+    <t>薬剤投与を行ったのは誰ですか？</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1228,13 +1228,13 @@
     <t>MedicationAdministration.reasonCode</t>
   </si>
   <si>
-    <t xml:space="preserve">理由に基づく行政処理 </t>
+    <t>理由に基づく行政処理</t>
   </si>
   <si>
     <t>与えられた薬を説明するコード。</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
+    <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1256,13 +1256,13 @@
 </t>
   </si>
   <si>
-    <t>「薬が投与された理由を支持する状態または観察」</t>
+    <t>薬が投与された理由を支持する状態または観察</t>
   </si>
   <si>
     <t>薬剤が投与された理由を支持する状態または観察。</t>
   </si>
   <si>
-    <t>「これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。」</t>
+    <t>これは、薬剤依頼の理由となる状態に関する参照です。もしコードしか存在しない場合は、reasonCodeを使用してください。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1284,13 +1284,13 @@
 </t>
   </si>
   <si>
-    <t>"リクエスト管理対象として実行してください。" (Rikuesuto kanri taishou toshite jikkou shite kudasai.)</t>
-  </si>
-  <si>
-    <t>「管理を実行するための元の要求、指示、または権限。」</t>
-  </si>
-  <si>
-    <t>「これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。」</t>
+    <t>リクエスト管理対象として実行してください。</t>
+  </si>
+  <si>
+    <t>管理を実行するための元の要求、指示、または権限。</t>
+  </si>
+  <si>
+    <t>これは、意図がオーダーまたはインスタンスオーダーであるMedicationRequestへの参照であり、意図が他の値であるMedicationRequestへの参照ではありません。</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1309,7 +1309,7 @@
 </t>
   </si>
   <si>
-    <t>「投与するための装置」</t>
+    <t>投与するための装置</t>
   </si>
   <si>
     <t>患者に薬剤を投与するのに使われる装置。例えば、特定の注入ポンプ。</t>
@@ -1328,10 +1328,10 @@
 </t>
   </si>
   <si>
-    <t>「行政に関する情報」</t>
-  </si>
-  <si>
-    <t>「他の属性では伝えられない薬剤投与に関する追加情報」</t>
+    <t>行政に関する情報</t>
+  </si>
+  <si>
+    <t>他の属性では伝えられない薬剤投与に関する追加情報</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1627,7 +1627,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -1897,17 +1897,13 @@
     <t>1回の投与イベントで投与される薬剤の量。この値は、投与が錠剤の飲み込みや注射などの本質的に瞬間的なイベントである場合に使用する。</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>RXA-6 Administered Amount / RXA-7 Administered Units</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]</t>
@@ -1950,17 +1946,13 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
+    <t>時間当たりの投与量</t>
+  </si>
+  <si>
+    <t>患者に投与されたあるいは投与される薬剤の導入速度を特定します。通常、投与速度は、100 ml / 1時間、または100 ml /時間（時間あたり100 ml）のような輸液の速度として表されます。時間単位あたりの速度として表される場合もあります。例えば、500 ml / 2時間のように。その他の例：200 mcg /分あるいは1分間当たり200 mcg；1リットル/8時間。</t>
+  </si>
+  <si>
+    <t>もしレートが時間の経過とともに変化する場合、かつそれをMedicationAdministrationに取り込む場合は、それぞれの変化を特定のMedicationAdministration.dosage.rateと、レート変更が発生した日時で捉える必要があります。通常、MedicationAdministration.dosage.rate要素は平均レートを伝えるために使用されません。</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]:rateQuantity</t>
@@ -1974,9 +1966,6 @@
   </si>
   <si>
     <t>投与速度(流量)を指定する単位は流量を表す単位（e.g. 量/時間)を指定する</t>
-  </si>
-  <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
   </si>
   <si>
     <t>MedicationAdministration.eventHistory</t>
@@ -14120,22 +14109,22 @@
         <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AK101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AM101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14143,10 +14132,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14169,16 +14158,16 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14216,17 +14205,17 @@
         <v>79</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14244,13 +14233,13 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -14258,13 +14247,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14286,10 +14275,10 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>621</v>
@@ -14345,7 +14334,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14354,22 +14343,22 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>623</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>132</v>
+        <v>616</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
@@ -14377,13 +14366,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -14405,16 +14394,16 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14464,7 +14453,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14473,22 +14462,22 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>606</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -14496,10 +14485,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14522,16 +14511,16 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14581,7 +14570,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14599,7 +14588,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -2291,17 +2291,17 @@
   <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.83203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.4140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="95.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2310,27 +2310,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="101.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="22.50390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10275,7 +10275,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -268,7 +268,7 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -812,7 +812,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -971,7 +971,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +995,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1037,7 +1037,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1062,7 +1062,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1209,7 +1209,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1252,7 +1252,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1910,7 +1910,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1971,7 +1971,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.2.0}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1451,7 +1451,7 @@
     <t>フリーテキストの投与方法の説明　SIG:用法</t>
   </si>
   <si>
-    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコーディングできない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
+    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコード化できない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
 投与量や用法のこの指示は、実際に投与される薬の投与量や用法を反映する必要がある。</t>
   </si>
   <si>
@@ -1676,7 +1676,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -576,7 +576,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
